--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484749_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484749_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. LADSON BUGALLO</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9444</v>
+        <v>6.1389</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7037</v>
+        <v>3.1699</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2408</v>
+        <v>2.969</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8435</v>
+        <v>4.1307</v>
       </c>
       <c r="H2" t="n">
-        <v>4.0859</v>
+        <v>-0.4046</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.2424</v>
+        <v>4.5353</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4638</v>
+        <v>5.0152</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7149</v>
+        <v>-0.126</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7489</v>
+        <v>5.1413</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6203</v>
+        <v>-0.8845</v>
       </c>
       <c r="N2" t="n">
-        <v>0.371</v>
+        <v>-0.2786</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.9913</v>
+        <v>-0.6059</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3774</v>
+        <v>2.6418</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.2079</v>
+        <v>-0.3774</v>
       </c>
       <c r="R2" t="n">
-        <v>3.5853</v>
+        <v>3.0192</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4784</v>
+        <v>-0.9544</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2026</v>
+        <v>-0.8263</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2758</v>
+        <v>-0.1281</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2452</v>
+        <v>0.3208</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2452</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.9624</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>W. LADSON BUGALLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1722</v>
+        <v>5.142</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4678</v>
+        <v>2.5361</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7045</v>
+        <v>2.6059</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1307</v>
+        <v>2.8435</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4046</v>
+        <v>4.0859</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5353</v>
+        <v>-1.2424</v>
       </c>
       <c r="J3" t="n">
-        <v>5.0152</v>
+        <v>4.4638</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.126</v>
+        <v>3.7149</v>
       </c>
       <c r="L3" t="n">
-        <v>5.1413</v>
+        <v>0.7489</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8845</v>
+        <v>-1.6203</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2786</v>
+        <v>0.371</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6059</v>
+        <v>-1.9913</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6418</v>
+        <v>0.3774</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3774</v>
+        <v>-3.2079</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0192</v>
+        <v>3.5853</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9211</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5285</v>
+        <v>0.035</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3926</v>
+        <v>0.6409</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3208</v>
+        <v>1.2452</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.2452</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.78</v>
+        <v>1.3122</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3598</v>
+        <v>0.2624</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4202</v>
+        <v>1.0498</v>
       </c>
       <c r="G4" t="n">
         <v>0.7722</v>
@@ -766,13 +766,13 @@
         <v>1.1322</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5173</v>
+        <v>0.0495</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2504</v>
+        <v>0.153</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2669</v>
+        <v>-0.1034</v>
       </c>
       <c r="V4" t="n">
         <v>0.3018</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6102</v>
+        <v>1.2233</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2975</v>
+        <v>0.2098</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9077</v>
+        <v>1.0135</v>
       </c>
       <c r="G5" t="n">
         <v>0.3184</v>
@@ -844,13 +844,13 @@
         <v>1.6983</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7648</v>
+        <v>-0.1517</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.117</v>
+        <v>-0.6097</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3521</v>
+        <v>0.458</v>
       </c>
       <c r="V5" t="n">
         <v>0.3018</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5473</v>
+        <v>-1.6238</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7938</v>
+        <v>-1.2407</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.3831</v>
       </c>
       <c r="G6" t="n">
         <v>-1.5359</v>
@@ -922,13 +922,13 @@
         <v>2.2644</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4414</v>
+        <v>0.3649</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4913</v>
+        <v>0.0444</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0499</v>
+        <v>0.3204</v>
       </c>
       <c r="V6" t="n">
         <v>-1.585</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3758</v>
+        <v>-2.6871</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9099</v>
+        <v>-2.5387</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4659</v>
+        <v>-0.1484</v>
       </c>
       <c r="G7" t="n">
         <v>-3.1043</v>
@@ -1000,13 +1000,13 @@
         <v>1.887</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1775</v>
+        <v>-0.4888</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4674</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7101</v>
+        <v>-0.3926</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6036</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.8964</v>
+        <v>-3.4718</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.8329</v>
+        <v>-3.5406</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0635</v>
+        <v>0.0688</v>
       </c>
       <c r="G8" t="n">
         <v>-3.2713</v>
@@ -1078,13 +1078,13 @@
         <v>1.1322</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.512</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.458</v>
+        <v>-0.1657</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0541</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3018</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3472</v>
+        <v>-4.3438</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.369</v>
+        <v>-4.154</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0218</v>
+        <v>-0.1898</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1103</v>
@@ -1156,13 +1156,13 @@
         <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1405</v>
+        <v>0.1439</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4703</v>
+        <v>-0.2553</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6108</v>
+        <v>0.3992</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2452</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.7728</v>
+        <v>-5.5402</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.0682</v>
+        <v>-5.6768</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2954</v>
+        <v>0.1366</v>
       </c>
       <c r="G10" t="n">
         <v>-5.7629</v>
@@ -1234,13 +1234,13 @@
         <v>2.4531</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3674</v>
+        <v>0.6</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.4288</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1875</v>
+        <v>1.0288</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9434</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5542</v>
+        <v>-5.6668</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.8242</v>
+        <v>-7.122</v>
       </c>
       <c r="F11" t="n">
-        <v>1.27</v>
+        <v>1.4552</v>
       </c>
       <c r="G11" t="n">
         <v>-3.2392</v>
@@ -1312,13 +1312,13 @@
         <v>2.6418</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5037</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3398</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1639</v>
+        <v>0.0212</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2452</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.9869</v>
+        <v>-9.517100000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.5642</v>
+        <v>-18.0946</v>
       </c>
       <c r="F12" t="n">
         <v>8.577499999999999</v>
@@ -1390,13 +1390,13 @@
         <v>20.757</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9341</v>
+        <v>-0.4646000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.2568</v>
+        <v>-2.7872</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3225</v>
+        <v>2.3226</v>
       </c>
       <c r="V12" t="n">
         <v>-3.7546</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.868</v>
+        <v>5.2331</v>
       </c>
       <c r="E13" t="n">
         <v>2.0003</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8677</v>
+        <v>3.2328</v>
       </c>
       <c r="G13" t="n">
         <v>2.4353</v>
@@ -1468,13 +1468,13 @@
         <v>2.4531</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4703</v>
+        <v>0.8354</v>
       </c>
       <c r="T13" t="n">
         <v>-0.3716</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8419</v>
+        <v>1.207</v>
       </c>
       <c r="V13" t="n">
         <v>0.6415999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6952</v>
+        <v>4.1174</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2364</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4588</v>
+        <v>3.5887</v>
       </c>
       <c r="G14" t="n">
         <v>5.9691</v>
@@ -1546,13 +1546,13 @@
         <v>2.0757</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1793</v>
+        <v>0.243</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1634</v>
+        <v>-0.8711</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9842</v>
+        <v>1.1141</v>
       </c>
       <c r="V14" t="n">
         <v>-0.019</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. AGBEKO</t>
+          <t>T. DESPLACE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2822</v>
+        <v>3.3993</v>
       </c>
       <c r="E15" t="n">
-        <v>0.264</v>
+        <v>1.3224</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0182</v>
+        <v>2.0768</v>
       </c>
       <c r="G15" t="n">
-        <v>4.2433</v>
+        <v>4.406</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4008</v>
+        <v>2.5552</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8425</v>
+        <v>1.8509</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8341</v>
+        <v>4.1267</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0784</v>
+        <v>2.1028</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7557</v>
+        <v>2.0239</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4092</v>
+        <v>0.2793</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3225</v>
+        <v>0.4524</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0868</v>
+        <v>-0.173</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5096</v>
+        <v>-3.3966</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.0192</v>
+        <v>-5.0949</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5096</v>
+        <v>1.6983</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2087</v>
+        <v>0.2012</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.1998</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.401</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3398</v>
+        <v>2.1886</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.4904</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3398</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. DESPLACE</t>
+          <t>R. AGBEKO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.054</v>
+        <v>3.3629</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0301</v>
+        <v>0.5563</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0239</v>
+        <v>2.8066</v>
       </c>
       <c r="G16" t="n">
-        <v>4.406</v>
+        <v>4.2433</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5552</v>
+        <v>1.4008</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8509</v>
+        <v>2.8425</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1267</v>
+        <v>3.8341</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1028</v>
+        <v>1.0784</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0239</v>
+        <v>2.7557</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2793</v>
+        <v>0.4092</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4524</v>
+        <v>0.3225</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.173</v>
+        <v>0.0868</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.3966</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.0949</v>
+        <v>-3.0192</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6983</v>
+        <v>1.5096</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.144</v>
+        <v>0.2894</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4921</v>
+        <v>-0.2586</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3481</v>
+        <v>0.548</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1886</v>
+        <v>0.3398</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4904</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3018</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9044</v>
+        <v>1.1762</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3766</v>
+        <v>-1.1817</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2809</v>
+        <v>2.3579</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6213</v>
@@ -1780,13 +1780,13 @@
         <v>1.887</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4744</v>
+        <v>-0.2025</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1634</v>
+        <v>-0.9685</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6891</v>
+        <v>0.7661</v>
       </c>
       <c r="V17" t="n">
         <v>1.2452</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.299</v>
+        <v>-0.2016</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.143</v>
+        <v>-0.0455</v>
       </c>
       <c r="F18" t="n">
         <v>-0.156</v>
@@ -1858,10 +1858,10 @@
         <v>0.3774</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1052</v>
+        <v>0.2027</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0588</v>
+        <v>0.0386</v>
       </c>
       <c r="U18" t="n">
         <v>0.164</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1563</v>
+        <v>-0.7076</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.5694</v>
+        <v>-3.2771</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4131</v>
+        <v>2.5695</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6084000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>1.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5855</v>
+        <v>-0.1368</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9871</v>
+        <v>-0.6947</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4016</v>
+        <v>0.5579</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3398</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3358</v>
+        <v>-1.2169</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3159</v>
+        <v>-3.8031</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9801</v>
+        <v>2.5862</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4842</v>
@@ -2014,13 +2014,13 @@
         <v>2.2644</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2616</v>
+        <v>0.3805</v>
       </c>
       <c r="T20" t="n">
-        <v>0.643</v>
+        <v>0.1558</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3815</v>
+        <v>0.2246</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3018</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.026</v>
+        <v>-3.5265</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7035</v>
+        <v>-4.6779</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6775</v>
+        <v>1.1513</v>
       </c>
       <c r="G21" t="n">
         <v>-3.0897</v>
@@ -2092,13 +2092,13 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2715</v>
+        <v>0.7709</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8217</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5502</v>
+        <v>-0.0764</v>
       </c>
       <c r="V21" t="n">
         <v>0.3018</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>10.9867</v>
+        <v>11.6363</v>
       </c>
       <c r="E22" t="n">
         <v>-8.5776</v>
       </c>
       <c r="F22" t="n">
-        <v>19.5642</v>
+        <v>20.2138</v>
       </c>
       <c r="G22" t="n">
         <v>10.959</v>
@@ -2170,13 +2170,13 @@
         <v>15.096</v>
       </c>
       <c r="S22" t="n">
-        <v>1.9341</v>
+        <v>2.5838</v>
       </c>
       <c r="T22" t="n">
         <v>-2.3226</v>
       </c>
       <c r="U22" t="n">
-        <v>4.2568</v>
+        <v>4.906300000000001</v>
       </c>
       <c r="V22" t="n">
         <v>3.7546</v>
